--- a/outputs/46897.xlsx
+++ b/outputs/46897.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
   <si>
     <t xml:space="preserve">Animals</t>
   </si>
@@ -56,9 +56,6 @@
   </si>
   <si>
     <t xml:space="preserve">Red </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
   </si>
   <si>
     <t xml:space="preserve">Rooster</t>
@@ -277,36 +274,40 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -582,239 +583,242 @@
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="1" style="1" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="23.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="7" t="n">
+        <f aca="false">COUNTIF(INDEX(A1:D15,0,MATCH(G1,A1:D1,0)),H2)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="C10" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <f aca="false">COUNTIF(INDEX(A:D,0,MATCH(I1,A1:D1,0)),I2)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="0" t="s">
+      <c r="C12" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="C13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="D14" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="0" t="s">
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>13</v>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/46897.xlsx
+++ b/outputs/46897.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="38">
   <si>
     <t xml:space="preserve">Animals</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t xml:space="preserve">Red </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
   </si>
   <si>
     <t xml:space="preserve">Rooster</t>
@@ -601,9 +604,6 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="H1" s="3" t="s">
         <v>4</v>
       </c>
@@ -625,7 +625,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>6</v>
@@ -633,119 +633,119 @@
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I3" s="7" t="n">
-        <f aca="false">COUNTIF(INDEX(A1:D15,0,MATCH(G1,A1:D1,0)),H2)</f>
+        <f aca="false">COUNTIF(INDEX($A$1:$D$15,0,MATCH($I$1,$A$1:$D$1,0)),$I$2)</f>
         <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
@@ -753,72 +753,72 @@
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
